--- a/sox_daily_tracking_log.xlsx
+++ b/sox_daily_tracking_log.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R30"/>
+  <dimension ref="A1:S34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,6 +518,11 @@
       <c r="R1" t="inlineStr">
         <is>
           <t>Last_Updated_Time</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>YF_Index_Price</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1299,7 @@
         <v>0.5422695929298591</v>
       </c>
       <c r="L30" t="n">
-        <v>1.034428591314902</v>
+        <v>1.034428591314903</v>
       </c>
       <c r="M30" t="n">
         <v>1.02112118796327</v>
@@ -1312,6 +1317,209 @@
         <is>
           <t>2026-07-03 16:19:48</t>
         </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>12626.221</v>
+      </c>
+      <c r="C31" t="n">
+        <v>51.54583</v>
+      </c>
+      <c r="D31" t="n">
+        <v>26.19895178082191</v>
+      </c>
+      <c r="E31" t="n">
+        <v>49.81575658664247</v>
+      </c>
+      <c r="F31" t="n">
+        <v>25.63538962820493</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Jul 02, 2026</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>74.38</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.730073413357538</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.5635621526169814</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.034729441684751</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.021983756080576</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-22.83417</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:00:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>12626.221</v>
+      </c>
+      <c r="C32" t="n">
+        <v>51.54583</v>
+      </c>
+      <c r="D32" t="n">
+        <v>26.18112978082192</v>
+      </c>
+      <c r="E32" t="n">
+        <v>49.81575658664247</v>
+      </c>
+      <c r="F32" t="n">
+        <v>25.60753883662741</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Jul 02, 2026</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>74.38</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.730073413357538</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.573590944194514</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.034729441684751</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.022399299981695</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-22.83417</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>2026-07-05 10:00:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>12626.221</v>
+      </c>
+      <c r="C33" t="n">
+        <v>51.54583</v>
+      </c>
+      <c r="D33" t="n">
+        <v>26.16361257534247</v>
+      </c>
+      <c r="E33" t="n">
+        <v>49.81575658664247</v>
+      </c>
+      <c r="F33" t="n">
+        <v>25.57974849467187</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Jul 02, 2026</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>74.38</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.730073413357538</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.5838640806705939</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.034729441684751</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.022825247120479</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-22.83417</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>2026-07-06 10:00:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>49.15125264480251</v>
+      </c>
+      <c r="F34" t="n">
+        <v>25.11654259125032</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Jul 06, 2026</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>71.37</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>2026-07-08 09:07:35</t>
+        </is>
+      </c>
+      <c r="S34" t="n">
+        <v>12300.516</v>
       </c>
     </row>
   </sheetData>

--- a/sox_daily_tracking_log.xlsx
+++ b/sox_daily_tracking_log.xlsx
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>49.15125264480251</v>
+        <v>49.21712288024855</v>
       </c>
       <c r="F34" t="n">
-        <v>25.11654259125032</v>
+        <v>25.11278486041417</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-07-08 09:07:35</t>
+          <t>2026-07-08 11:00:25</t>
         </is>
       </c>
       <c r="S34" t="n">

--- a/sox_daily_tracking_log.xlsx
+++ b/sox_daily_tracking_log.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S34"/>
+  <dimension ref="A1:S35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1522,6 +1522,41 @@
         <v>12300.516</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>48.69054808487731</v>
+      </c>
+      <c r="F35" t="n">
+        <v>25.39485351789734</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Jul 07, 2026</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:28:35</t>
+        </is>
+      </c>
+      <c r="S35" t="n">
+        <v>12574.967</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sox_daily_tracking_log.xlsx
+++ b/sox_daily_tracking_log.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S35"/>
+  <dimension ref="A1:S37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1532,7 +1532,7 @@
         <v>48.69054808487731</v>
       </c>
       <c r="F35" t="n">
-        <v>25.39485351789734</v>
+        <v>25.39485351789733</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1555,6 +1555,76 @@
       </c>
       <c r="S35" t="n">
         <v>12574.967</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>50.82913292467362</v>
+      </c>
+      <c r="F36" t="n">
+        <v>25.5801812844072</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Jul 13, 2026</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>72.88</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>2026-07-14 23:32:56</t>
+        </is>
+      </c>
+      <c r="S36" t="n">
+        <v>12758.711</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>49.22843746021451</v>
+      </c>
+      <c r="F37" t="n">
+        <v>25.4242751021675</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Jul 13, 2026</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>72.88</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>2026-07-15 11:00:33</t>
+        </is>
+      </c>
+      <c r="S37" t="n">
+        <v>12661.931</v>
       </c>
     </row>
   </sheetData>

--- a/sox_daily_tracking_log.xlsx
+++ b/sox_daily_tracking_log.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S37"/>
+  <dimension ref="A1:S42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1627,6 +1627,181 @@
         <v>12661.931</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>50.04296187410337</v>
+      </c>
+      <c r="F38" t="n">
+        <v>24.80976144657198</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Jul 14, 2026</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>70.31999999999999</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>2026-07-16 13:41:12</t>
+        </is>
+      </c>
+      <c r="S38" t="n">
+        <v>12398.894</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>48.45814065677336</v>
+      </c>
+      <c r="F39" t="n">
+        <v>23.53120677700344</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Jul 15, 2026</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>71.20999999999999</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>2026-07-17 13:35:42</t>
+        </is>
+      </c>
+      <c r="S39" t="n">
+        <v>11867.503</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>45.89766557536202</v>
+      </c>
+      <c r="F40" t="n">
+        <v>23.19046216061464</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Jul 16, 2026</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>2026-07-18 10:00:30</t>
+        </is>
+      </c>
+      <c r="S40" t="n">
+        <v>11673.889</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>45.71347264615592</v>
+      </c>
+      <c r="F41" t="n">
+        <v>23.11395052809082</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Jul 17, 2026</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:34:04</t>
+        </is>
+      </c>
+      <c r="S41" t="n">
+        <v>11673.889</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>45.71347264615592</v>
+      </c>
+      <c r="F42" t="n">
+        <v>23.08913898855713</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Jul 17, 2026</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>2026-07-20 12:46:44</t>
+        </is>
+      </c>
+      <c r="S42" t="n">
+        <v>11673.889</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sox_daily_tracking_log.xlsx
+++ b/sox_daily_tracking_log.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S42"/>
+  <dimension ref="A1:S45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1802,6 +1802,94 @@
         <v>11673.889</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>2026-07-22 11:07:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>49.0272978491043</v>
+      </c>
+      <c r="F44" t="n">
+        <v>24.23522952761116</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Jul 22, 2026</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>69.78</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>2026-07-24 10:13:10</t>
+        </is>
+      </c>
+      <c r="S44" t="n">
+        <v>12343.837</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>46.48041045417513</v>
+      </c>
+      <c r="F45" t="n">
+        <v>21.27467984123194</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Jul 27, 2026</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>66.98</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>2026-07-29 16:02:16</t>
+        </is>
+      </c>
+      <c r="S45" t="n">
+        <v>11035.683</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sox_daily_tracking_log.xlsx
+++ b/sox_daily_tracking_log.xlsx
@@ -1883,7 +1883,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-07-29 16:02:16</t>
+          <t>2026-07-29 16:05:31</t>
         </is>
       </c>
       <c r="S45" t="n">

--- a/sox_daily_tracking_log.xlsx
+++ b/sox_daily_tracking_log.xlsx
@@ -1883,7 +1883,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-07-29 16:05:31</t>
+          <t>2026-07-29 16:06:21</t>
         </is>
       </c>
       <c r="S45" t="n">

--- a/sox_daily_tracking_log.xlsx
+++ b/sox_daily_tracking_log.xlsx
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>46.48041045417513</v>
+        <v>46.35409915476403</v>
       </c>
       <c r="F45" t="n">
         <v>21.27467984123194</v>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-07-29 16:06:21</t>
+          <t>2026-07-29 17:33:02</t>
         </is>
       </c>
       <c r="S45" t="n">

--- a/sox_daily_tracking_log.xlsx
+++ b/sox_daily_tracking_log.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S45"/>
+  <dimension ref="A1:S46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1890,6 +1890,41 @@
         <v>11035.683</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>43.82695813854346</v>
+      </c>
+      <c r="F46" t="n">
+        <v>19.82268905561006</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Jul 28, 2026</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>66.34999999999999</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>2026-07-30 11:02:16</t>
+        </is>
+      </c>
+      <c r="S46" t="n">
+        <v>10447.489</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sox_daily_tracking_log.xlsx
+++ b/sox_daily_tracking_log.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S46"/>
+  <dimension ref="A1:S48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1925,6 +1925,76 @@
         <v>10447.489</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>45.21372668348384</v>
+      </c>
+      <c r="F47" t="n">
+        <v>21.41722036978813</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Jul 29, 2026</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>62.33</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>2026-07-31 10:00:27</t>
+        </is>
+      </c>
+      <c r="S47" t="n">
+        <v>11302.987</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>49.86077865414968</v>
+      </c>
+      <c r="F48" t="n">
+        <v>22.52990089036847</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Aug 04, 2026</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>63.06</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:00:23</t>
+        </is>
+      </c>
+      <c r="S48" t="n">
+        <v>12008.883</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sox_daily_tracking_log.xlsx
+++ b/sox_daily_tracking_log.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S48"/>
+  <dimension ref="A1:S49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1995,6 +1995,24 @@
         <v>12008.883</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:50:53</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sox_daily_tracking_log.xlsx
+++ b/sox_daily_tracking_log.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S49"/>
+  <dimension ref="A1:S50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2013,6 +2013,41 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>49.93141417838821</v>
+      </c>
+      <c r="F50" t="n">
+        <v>22.69483857942407</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Aug 06, 2026</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>2026-08-09 19:19:05</t>
+        </is>
+      </c>
+      <c r="S50" t="n">
+        <v>12356.787</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sox_daily_tracking_log.xlsx
+++ b/sox_daily_tracking_log.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S50"/>
+  <dimension ref="A1:S53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2048,6 +2048,94 @@
         <v>12356.787</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>49.07589330284966</v>
+      </c>
+      <c r="F51" t="n">
+        <v>22.20713314518042</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Aug 10, 2026</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>66.54000000000001</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>2026-08-12 11:06:38</t>
+        </is>
+      </c>
+      <c r="S51" t="n">
+        <v>12098.472</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>2026-08-23 22:49:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>44.83403092138953</v>
+      </c>
+      <c r="F53" t="n">
+        <v>21.04029791848937</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Aug 21, 2026</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>64.37</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:00:38</t>
+        </is>
+      </c>
+      <c r="S53" t="n">
+        <v>11740.374</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sox_daily_tracking_log.xlsx
+++ b/sox_daily_tracking_log.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S53"/>
+  <dimension ref="A1:S55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2136,6 +2136,76 @@
         <v>11740.374</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>44.93052769015844</v>
+      </c>
+      <c r="F54" t="n">
+        <v>21.02064495034362</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Aug 26, 2026</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>63.68</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>2026-08-27 22:21:43</t>
+        </is>
+      </c>
+      <c r="S54" t="n">
+        <v>11828.587</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>42.2437793567467</v>
+      </c>
+      <c r="F55" t="n">
+        <v>20.54419805259325</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Aug 27, 2026</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>63.45</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>2026-08-29 15:02:40</t>
+        </is>
+      </c>
+      <c r="S55" t="n">
+        <v>11469.662</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sox_daily_tracking_log.xlsx
+++ b/sox_daily_tracking_log.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S55"/>
+  <dimension ref="A1:S57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2206,6 +2206,76 @@
         <v>11469.662</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>41.02895420205375</v>
+      </c>
+      <c r="F56" t="n">
+        <v>19.58567146677364</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Sep 01, 2026</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>62.73</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>2026-09-03 18:58:56</t>
+        </is>
+      </c>
+      <c r="S56" t="n">
+        <v>11339.254</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>41.48834325339904</v>
+      </c>
+      <c r="F57" t="n">
+        <v>20.22488740004271</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Sep 03, 2026</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>61.85</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>2026-09-05 11:01:15</t>
+        </is>
+      </c>
+      <c r="S57" t="n">
+        <v>11735.263</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sox_daily_tracking_log.xlsx
+++ b/sox_daily_tracking_log.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S57"/>
+  <dimension ref="A1:S58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2276,6 +2276,41 @@
         <v>11735.263</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>42.69621477760009</v>
+      </c>
+      <c r="F58" t="n">
+        <v>20.38513315033006</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Sep 04, 2026</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>62.09</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>2026-09-09 17:41:44</t>
+        </is>
+      </c>
+      <c r="S58" t="n">
+        <v>11887.869</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sox_daily_tracking_log.xlsx
+++ b/sox_daily_tracking_log.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S58"/>
+  <dimension ref="A1:S59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2311,6 +2311,41 @@
         <v>11887.869</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>42.15578945810463</v>
+      </c>
+      <c r="F59" t="n">
+        <v>20.10633789866106</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Sep 10, 2026</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>64.62</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>2026-09-12 11:01:21</t>
+        </is>
+      </c>
+      <c r="S59" t="n">
+        <v>11823.998</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
